--- a/r4-core-ballot_2026_03/StructureDefinition-at-core-organization.xlsx
+++ b/r4-core-ballot_2026_03/StructureDefinition-at-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T09:17:47+00:00</t>
+    <t>2026-10-27T15:46:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
